--- a/artfynd/A 39356-2025 artfynd.xlsx
+++ b/artfynd/A 39356-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119628750</v>
+        <v>119628749</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,17 +695,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>611551</v>
+        <v>611520</v>
       </c>
       <c r="R2" t="n">
-        <v>6951567</v>
+        <v>6951657</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119628751</v>
+        <v>119628750</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,13 +825,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>611544</v>
+        <v>611551</v>
       </c>
       <c r="R3" t="n">
-        <v>6951565</v>
+        <v>6951567</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +900,7 @@
         <v>119628752</v>
       </c>
       <c r="B4" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,12 +917,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1020,6 +1005,117 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119628751</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Uddefors, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>611544</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6951565</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljustorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:56</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39356-2025 artfynd.xlsx
+++ b/artfynd/A 39356-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628749</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628750</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628752</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,8 +1136,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119628751</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>